--- a/dataset/DATASET TA.xlsx
+++ b/dataset/DATASET TA.xlsx
@@ -1,26 +1,29 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\Documents\SEMESTER 7\METOPEN\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\Documents\SEMESTER 8\METOPEN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{BBC4B492-AAAD-4A78-AF63-8A8428F5A4B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA32379D-2989-401F-94F1-A30BFCD78E88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{6DE54A4B-1076-4F32-948D-B8005E3F3282}"/>
   </bookViews>
   <sheets>
     <sheet name="DATASET TA" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'DATASET TA'!$A$1:$AG$451</definedName>
+  </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5434" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5433" uniqueCount="39">
   <si>
     <t>FS10</t>
   </si>
@@ -109,16 +112,7 @@
     <t>Sangat tidak setuju</t>
   </si>
   <si>
-    <t>Agak setuju</t>
-  </si>
-  <si>
     <t>Sangat Setuju</t>
-  </si>
-  <si>
-    <t>Saangat Setuju</t>
-  </si>
-  <si>
-    <t>1`</t>
   </si>
   <si>
     <t>FS1</t>
@@ -633,48 +627,48 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="42">
-    <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
-    <cellStyle name="20% - Accent2" xfId="23" builtinId="34" customBuiltin="1"/>
-    <cellStyle name="20% - Accent3" xfId="27" builtinId="38" customBuiltin="1"/>
-    <cellStyle name="20% - Accent4" xfId="31" builtinId="42" customBuiltin="1"/>
-    <cellStyle name="20% - Accent5" xfId="35" builtinId="46" customBuiltin="1"/>
-    <cellStyle name="20% - Accent6" xfId="39" builtinId="50" customBuiltin="1"/>
-    <cellStyle name="40% - Accent1" xfId="20" builtinId="31" customBuiltin="1"/>
-    <cellStyle name="40% - Accent2" xfId="24" builtinId="35" customBuiltin="1"/>
-    <cellStyle name="40% - Accent3" xfId="28" builtinId="39" customBuiltin="1"/>
-    <cellStyle name="40% - Accent4" xfId="32" builtinId="43" customBuiltin="1"/>
-    <cellStyle name="40% - Accent5" xfId="36" builtinId="47" customBuiltin="1"/>
-    <cellStyle name="40% - Accent6" xfId="40" builtinId="51" customBuiltin="1"/>
-    <cellStyle name="60% - Accent1" xfId="21" builtinId="32" customBuiltin="1"/>
-    <cellStyle name="60% - Accent2" xfId="25" builtinId="36" customBuiltin="1"/>
-    <cellStyle name="60% - Accent3" xfId="29" builtinId="40" customBuiltin="1"/>
-    <cellStyle name="60% - Accent4" xfId="33" builtinId="44" customBuiltin="1"/>
-    <cellStyle name="60% - Accent5" xfId="37" builtinId="48" customBuiltin="1"/>
-    <cellStyle name="60% - Accent6" xfId="41" builtinId="52" customBuiltin="1"/>
-    <cellStyle name="Accent1" xfId="18" builtinId="29" customBuiltin="1"/>
-    <cellStyle name="Accent2" xfId="22" builtinId="33" customBuiltin="1"/>
-    <cellStyle name="Accent3" xfId="26" builtinId="37" customBuiltin="1"/>
-    <cellStyle name="Accent4" xfId="30" builtinId="41" customBuiltin="1"/>
-    <cellStyle name="Accent5" xfId="34" builtinId="45" customBuiltin="1"/>
-    <cellStyle name="Accent6" xfId="38" builtinId="49" customBuiltin="1"/>
-    <cellStyle name="Bad" xfId="7" builtinId="27" customBuiltin="1"/>
-    <cellStyle name="Calculation" xfId="11" builtinId="22" customBuiltin="1"/>
-    <cellStyle name="Check Cell" xfId="13" builtinId="23" customBuiltin="1"/>
-    <cellStyle name="Explanatory Text" xfId="16" builtinId="53" customBuiltin="1"/>
-    <cellStyle name="Good" xfId="6" builtinId="26" customBuiltin="1"/>
-    <cellStyle name="Heading 1" xfId="2" builtinId="16" customBuiltin="1"/>
-    <cellStyle name="Heading 2" xfId="3" builtinId="17" customBuiltin="1"/>
-    <cellStyle name="Heading 3" xfId="4" builtinId="18" customBuiltin="1"/>
-    <cellStyle name="Heading 4" xfId="5" builtinId="19" customBuiltin="1"/>
-    <cellStyle name="Input" xfId="9" builtinId="20" customBuiltin="1"/>
-    <cellStyle name="Linked Cell" xfId="12" builtinId="24" customBuiltin="1"/>
-    <cellStyle name="Neutral" xfId="8" builtinId="28" customBuiltin="1"/>
+    <cellStyle name="20% - Aksen1" xfId="19" builtinId="30" customBuiltin="1"/>
+    <cellStyle name="20% - Aksen2" xfId="23" builtinId="34" customBuiltin="1"/>
+    <cellStyle name="20% - Aksen3" xfId="27" builtinId="38" customBuiltin="1"/>
+    <cellStyle name="20% - Aksen4" xfId="31" builtinId="42" customBuiltin="1"/>
+    <cellStyle name="20% - Aksen5" xfId="35" builtinId="46" customBuiltin="1"/>
+    <cellStyle name="20% - Aksen6" xfId="39" builtinId="50" customBuiltin="1"/>
+    <cellStyle name="40% - Aksen1" xfId="20" builtinId="31" customBuiltin="1"/>
+    <cellStyle name="40% - Aksen2" xfId="24" builtinId="35" customBuiltin="1"/>
+    <cellStyle name="40% - Aksen3" xfId="28" builtinId="39" customBuiltin="1"/>
+    <cellStyle name="40% - Aksen4" xfId="32" builtinId="43" customBuiltin="1"/>
+    <cellStyle name="40% - Aksen5" xfId="36" builtinId="47" customBuiltin="1"/>
+    <cellStyle name="40% - Aksen6" xfId="40" builtinId="51" customBuiltin="1"/>
+    <cellStyle name="60% - Aksen1" xfId="21" builtinId="32" customBuiltin="1"/>
+    <cellStyle name="60% - Aksen2" xfId="25" builtinId="36" customBuiltin="1"/>
+    <cellStyle name="60% - Aksen3" xfId="29" builtinId="40" customBuiltin="1"/>
+    <cellStyle name="60% - Aksen4" xfId="33" builtinId="44" customBuiltin="1"/>
+    <cellStyle name="60% - Aksen5" xfId="37" builtinId="48" customBuiltin="1"/>
+    <cellStyle name="60% - Aksen6" xfId="41" builtinId="52" customBuiltin="1"/>
+    <cellStyle name="Aksen1" xfId="18" builtinId="29" customBuiltin="1"/>
+    <cellStyle name="Aksen2" xfId="22" builtinId="33" customBuiltin="1"/>
+    <cellStyle name="Aksen3" xfId="26" builtinId="37" customBuiltin="1"/>
+    <cellStyle name="Aksen4" xfId="30" builtinId="41" customBuiltin="1"/>
+    <cellStyle name="Aksen5" xfId="34" builtinId="45" customBuiltin="1"/>
+    <cellStyle name="Aksen6" xfId="38" builtinId="49" customBuiltin="1"/>
+    <cellStyle name="Baik" xfId="6" builtinId="26" customBuiltin="1"/>
+    <cellStyle name="Buruk" xfId="7" builtinId="27" customBuiltin="1"/>
+    <cellStyle name="Catatan" xfId="15" builtinId="10" customBuiltin="1"/>
+    <cellStyle name="Judul" xfId="1" builtinId="15" customBuiltin="1"/>
+    <cellStyle name="Judul 1" xfId="2" builtinId="16" customBuiltin="1"/>
+    <cellStyle name="Judul 2" xfId="3" builtinId="17" customBuiltin="1"/>
+    <cellStyle name="Judul 3" xfId="4" builtinId="18" customBuiltin="1"/>
+    <cellStyle name="Judul 4" xfId="5" builtinId="19" customBuiltin="1"/>
+    <cellStyle name="Keluaran" xfId="10" builtinId="21" customBuiltin="1"/>
+    <cellStyle name="Masukan" xfId="9" builtinId="20" customBuiltin="1"/>
+    <cellStyle name="Netral" xfId="8" builtinId="28" customBuiltin="1"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Note" xfId="15" builtinId="10" customBuiltin="1"/>
-    <cellStyle name="Output" xfId="10" builtinId="21" customBuiltin="1"/>
-    <cellStyle name="Title" xfId="1" builtinId="15" customBuiltin="1"/>
+    <cellStyle name="Perhitungan" xfId="11" builtinId="22" customBuiltin="1"/>
+    <cellStyle name="Sel Periksa" xfId="13" builtinId="23" customBuiltin="1"/>
+    <cellStyle name="Sel Tertaut" xfId="12" builtinId="24" customBuiltin="1"/>
+    <cellStyle name="Teks Penjelasan" xfId="16" builtinId="53" customBuiltin="1"/>
+    <cellStyle name="Teks Peringatan" xfId="14" builtinId="11" customBuiltin="1"/>
     <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
-    <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -690,7 +684,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema Office">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -991,31 +985,31 @@
   <sheetData>
     <row r="1" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D1" t="s">
         <v>33</v>
       </c>
-      <c r="B1" t="s">
+      <c r="E1" t="s">
         <v>34</v>
       </c>
-      <c r="C1" t="s">
+      <c r="F1" t="s">
         <v>35</v>
       </c>
-      <c r="D1" t="s">
+      <c r="G1" t="s">
         <v>36</v>
       </c>
-      <c r="E1" t="s">
+      <c r="H1" t="s">
         <v>37</v>
       </c>
-      <c r="F1" t="s">
+      <c r="I1" t="s">
         <v>38</v>
-      </c>
-      <c r="G1" t="s">
-        <v>39</v>
-      </c>
-      <c r="H1" t="s">
-        <v>40</v>
-      </c>
-      <c r="I1" t="s">
-        <v>41</v>
       </c>
       <c r="J1" t="s">
         <v>0</v>
@@ -25938,7 +25932,7 @@
     </row>
     <row r="248" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A248" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B248" t="s">
         <v>24</v>
@@ -25956,7 +25950,7 @@
         <v>26</v>
       </c>
       <c r="G248" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H248" t="s">
         <v>26</v>
@@ -26140,7 +26134,7 @@
     </row>
     <row r="250" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A250" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B250" t="s">
         <v>24</v>
@@ -29087,7 +29081,7 @@
         <v>26</v>
       </c>
       <c r="G279" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="H279" t="s">
         <v>26</v>
@@ -29586,7 +29580,7 @@
         <v>24</v>
       </c>
       <c r="E284" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="F284" t="s">
         <v>26</v>
@@ -30810,16 +30804,16 @@
         <v>26</v>
       </c>
       <c r="I296" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="J296" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="K296" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="L296" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="M296">
         <v>1</v>
@@ -33709,8 +33703,8 @@
       <c r="AF324">
         <v>2</v>
       </c>
-      <c r="AG324" t="s">
-        <v>32</v>
+      <c r="AG324">
+        <v>1</v>
       </c>
     </row>
     <row r="325" spans="1:33" x14ac:dyDescent="0.35">
@@ -36300,7 +36294,7 @@
         <v>1</v>
       </c>
       <c r="U350">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="V350">
         <v>1</v>
@@ -46541,6 +46535,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:AG451" xr:uid="{BB1F47D4-FE18-4115-826C-1551D70A186A}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>